--- a/exports/CIPLA_full_report.xlsx
+++ b/exports/CIPLA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.45</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>897</v>
+        <v>885.2</v>
       </c>
       <c r="I2" t="n">
         <v>892.4628580585</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.17</v>
+        <v>-3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="M2" t="n">
         <v>0.58</v>
       </c>
       <c r="N2" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="O2" t="n">
         <v>0.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>4.36</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44585.55208333334</v>
+        <v>44586.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>892.3</v>
+        <v>898.9</v>
       </c>
       <c r="I3" t="n">
         <v>898.35801215178</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8</v>
+        <v>-1.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="M3" t="n">
         <v>0.48</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>5.26</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.55208333334</v>
+        <v>44607.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>955</v>
+        <v>927.95</v>
       </c>
       <c r="I4" t="n">
         <v>935.4615989083587</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>6.24</v>
+        <v>3.23</v>
       </c>
       <c r="L4" t="n">
         <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>1.74</v>
+        <v>4.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>3.57</v>
       </c>
       <c r="O4" t="n">
         <v>1.09</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.07</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>923.2</v>
+        <v>939</v>
       </c>
       <c r="I5" t="n">
         <v>938.1492519501896</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>0.51</v>
+        <v>-1.19</v>
       </c>
       <c r="L5" t="n">
         <v>2.94</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.95</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1016.6</v>
+        <v>988.75</v>
       </c>
       <c r="I6" t="n">
         <v>1001.531440318861</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>8.26</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
         <v>2.32</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>7.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>936.2</v>
+        <v>975.2</v>
       </c>
       <c r="I7" t="n">
         <v>974.3472344377235</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>5.31</v>
+        <v>1.37</v>
       </c>
       <c r="L7" t="n">
         <v>3.16</v>
       </c>
       <c r="M7" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>4.25</v>
       </c>
       <c r="O7" t="n">
         <v>-3.98</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.29</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>966.4</v>
+        <v>931.2</v>
       </c>
       <c r="I8" t="n">
         <v>952.0858166053777</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9</v>
+        <v>-4.51</v>
       </c>
       <c r="L8" t="n">
-        <v>3.71</v>
+        <v>4.85</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>960.5</v>
+        <v>978.45</v>
       </c>
       <c r="I9" t="n">
         <v>971.7492272318053</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.15</v>
+        <v>-5.07</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>5.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.08</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1043.9</v>
+        <v>1024.5</v>
       </c>
       <c r="I10" t="n">
         <v>1026.384174629609</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K10" t="n">
-        <v>6.69</v>
+        <v>4.71</v>
       </c>
       <c r="L10" t="n">
         <v>3.47</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>5.47</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44824.38541666666</v>
+        <v>44824.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1073.6</v>
+        <v>1095</v>
       </c>
       <c r="I11" t="n">
         <v>1080.564072173685</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.79</v>
+        <v>-6.88</v>
       </c>
       <c r="L11" t="n">
-        <v>5.01</v>
+        <v>7.08</v>
       </c>
       <c r="M11" t="n">
         <v>0.78</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.66</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44869.55208333334</v>
+        <v>44872.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1146.05</v>
+        <v>1120.95</v>
       </c>
       <c r="I12" t="n">
         <v>1132.134225868499</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>4.66</v>
+        <v>2.37</v>
       </c>
       <c r="L12" t="n">
         <v>4.02</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.14</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1128.15</v>
+        <v>1142.9</v>
       </c>
       <c r="I13" t="n">
         <v>1135.910410252628</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.64</v>
+        <v>-1.96</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>4.43</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1096.65</v>
+        <v>1090.35</v>
       </c>
       <c r="I14" t="n">
         <v>1092.22848233094</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.05</v>
+        <v>-4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>4.79</v>
+        <v>4.97</v>
       </c>
       <c r="M14" t="n">
         <v>0.53</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>3.37</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1112.75</v>
+        <v>1129.5</v>
       </c>
       <c r="I15" t="n">
         <v>1124.465141949385</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.05</v>
+        <v>-3.59</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>3.64</v>
       </c>
       <c r="M15" t="n">
         <v>0.2</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.16</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44922.55208333334</v>
+        <v>44923.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1097.95</v>
+        <v>1086.7</v>
       </c>
       <c r="I16" t="n">
         <v>1088.171724330308</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.79</v>
+        <v>-3.79</v>
       </c>
       <c r="L16" t="n">
-        <v>3.47</v>
+        <v>3.85</v>
       </c>
       <c r="M16" t="n">
         <v>0.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.02</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45012.55208333334</v>
+        <v>45013.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>890</v>
+        <v>893.15</v>
       </c>
       <c r="I17" t="n">
         <v>891.3491498037735</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>89.16666666666667</v>
+        <v>90</v>
       </c>
       <c r="K17" t="n">
-        <v>18.1</v>
+        <v>17.81</v>
       </c>
       <c r="L17" t="n">
         <v>1.49</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.4</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45058.55208333334</v>
+        <v>45061.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="I18" t="n">
         <v>917.367469153656</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K18" t="n">
-        <v>4.46</v>
+        <v>2.45</v>
       </c>
       <c r="L18" t="n">
         <v>0.87</v>
@@ -1467,7 +1682,7 @@
         <v>0.24</v>
       </c>
       <c r="N18" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="O18" t="n">
         <v>-0.08</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.56</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>950</v>
+        <v>952.95</v>
       </c>
       <c r="I19" t="n">
         <v>952.6682402487015</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.83</v>
+        <v>-4.15</v>
       </c>
       <c r="L19" t="n">
-        <v>4.13</v>
+        <v>4.37</v>
       </c>
       <c r="M19" t="n">
         <v>0.8</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.26</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45190.55208333334</v>
+        <v>45191.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1209.1</v>
+        <v>1188.2</v>
       </c>
       <c r="I20" t="n">
         <v>1201.111527797696</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>115.1666666666667</v>
+        <v>116</v>
       </c>
       <c r="K20" t="n">
-        <v>26.88</v>
+        <v>24.69</v>
       </c>
       <c r="L20" t="n">
         <v>1.12</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>162</v>
+        <v>163</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45216.55208333334</v>
+        <v>45217.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1172</v>
+        <v>1214.65</v>
       </c>
       <c r="I21" t="n">
         <v>1192.362048815934</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>1.36</v>
+        <v>-2.23</v>
       </c>
       <c r="L21" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
         <v>1.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.12</v>
+        <v>3.63</v>
       </c>
       <c r="O21" t="n">
         <v>-1.91</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5.38</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1185.7</v>
+        <v>1156.2</v>
       </c>
       <c r="I22" t="n">
         <v>1170.836451742745</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.38</v>
+        <v>-4.81</v>
       </c>
       <c r="L22" t="n">
-        <v>3.17</v>
+        <v>4.96</v>
       </c>
       <c r="M22" t="n">
         <v>0.33</v>
       </c>
       <c r="N22" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
         <v>3.63</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>6.13</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45226.55208333334</v>
+        <v>45229.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1176</v>
+        <v>1199.2</v>
       </c>
       <c r="I23" t="n">
         <v>1199.161984751945</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.71</v>
+        <v>-3.72</v>
       </c>
       <c r="L23" t="n">
-        <v>3.61</v>
+        <v>4.86</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="N23" t="n">
         <v>2.08</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.72</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45252.55208333334</v>
+        <v>45253.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1272.9</v>
+        <v>1185.85</v>
       </c>
       <c r="I24" t="n">
         <v>1232.339512086002</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>6.15</v>
+        <v>-1.11</v>
       </c>
       <c r="L24" t="n">
         <v>1.81</v>
@@ -1809,7 +2096,7 @@
         <v>0.54</v>
       </c>
       <c r="N24" t="n">
-        <v>0.48</v>
+        <v>7.74</v>
       </c>
       <c r="O24" t="n">
         <v>1.57</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.51</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45279.38541666666</v>
+        <v>45279.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1224.6</v>
+        <v>1240</v>
       </c>
       <c r="I25" t="n">
         <v>1238.935495210338</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.27</v>
+        <v>-4.57</v>
       </c>
       <c r="L25" t="n">
         <v>7.1</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.28</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45321.38541666666</v>
+        <v>45321.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1329.8</v>
+        <v>1318</v>
       </c>
       <c r="I26" t="n">
         <v>1329.155693782879</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>7.24</v>
+        <v>6.29</v>
       </c>
       <c r="L26" t="n">
         <v>2.75</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>6.67</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1391</v>
+        <v>1439.25</v>
       </c>
       <c r="I27" t="n">
         <v>1405.881799290333</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.54</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>6.58</v>
+        <v>9.23</v>
       </c>
       <c r="M27" t="n">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="N27" t="n">
-        <v>2.58</v>
+        <v>2.98</v>
       </c>
       <c r="O27" t="n">
         <v>-1.76</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.05</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45370.38541666666</v>
+        <v>45370.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1450.35</v>
+        <v>1434.95</v>
       </c>
       <c r="I28" t="n">
         <v>1443.236846190422</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>0.77</v>
+        <v>-0.3</v>
       </c>
       <c r="L28" t="n">
         <v>3.12</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.89</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1469.35</v>
+        <v>1496.9</v>
       </c>
       <c r="I29" t="n">
         <v>1491.596575626147</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.4</v>
+        <v>-4.32</v>
       </c>
       <c r="L29" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>6.02</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45391.55208333334</v>
+        <v>45392.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1449</v>
+        <v>1407.25</v>
       </c>
       <c r="I30" t="n">
         <v>1432.854464733398</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.2</v>
+        <v>-5.99</v>
       </c>
       <c r="L30" t="n">
-        <v>3.97</v>
+        <v>6.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.31</v>
       </c>
       <c r="N30" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="O30" t="n">
         <v>1.81</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>6.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1401</v>
+        <v>1413.55</v>
       </c>
       <c r="I31" t="n">
         <v>1410.879268606303</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K31" t="n">
-        <v>0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="L31" t="n">
         <v>3.41</v>
       </c>
       <c r="M31" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="N31" t="n">
         <v>3.78</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>4.68</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1385.9</v>
+        <v>1370.2</v>
       </c>
       <c r="I32" t="n">
         <v>1370.841575386965</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.96</v>
+        <v>-3.07</v>
       </c>
       <c r="L32" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.19</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1403</v>
+        <v>1425.8</v>
       </c>
       <c r="I33" t="n">
         <v>1423.338814559776</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.39</v>
+        <v>-4.06</v>
       </c>
       <c r="L33" t="n">
         <v>4.25</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.77</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45464.55208333334</v>
+        <v>45467.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1537.25</v>
+        <v>1510.95</v>
       </c>
       <c r="I34" t="n">
         <v>1513.961816920772</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K34" t="n">
-        <v>7.82</v>
+        <v>5.97</v>
       </c>
       <c r="L34" t="n">
         <v>2.06</v>
       </c>
       <c r="M34" t="n">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="N34" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="O34" t="n">
         <v>2.67</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>4.18</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1500</v>
+        <v>1531</v>
       </c>
       <c r="I35" t="n">
         <v>1527.060797621359</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K35" t="n">
-        <v>0.72</v>
+        <v>-1.33</v>
       </c>
       <c r="L35" t="n">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="M35" t="n">
         <v>0.4</v>
       </c>
       <c r="N35" t="n">
-        <v>1.69</v>
+        <v>5.77</v>
       </c>
       <c r="O35" t="n">
         <v>-1.91</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>4.57</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45560.55208333334</v>
+        <v>45561.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1648</v>
+        <v>1605.8</v>
       </c>
       <c r="I36" t="n">
         <v>1618.689918969259</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K36" t="n">
-        <v>7.64</v>
+        <v>4.89</v>
       </c>
       <c r="L36" t="n">
         <v>3.85</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.13</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45595.55208333334</v>
+        <v>45596.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1418</v>
+        <v>1559.6</v>
       </c>
       <c r="I37" t="n">
         <v>1507.496713104003</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K37" t="n">
-        <v>11.7</v>
+        <v>2.88</v>
       </c>
       <c r="L37" t="n">
         <v>5.99</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6899999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>9.52</v>
       </c>
       <c r="O37" t="n">
         <v>-1.76</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45609.38541666666</v>
+        <v>45609.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1518.1</v>
+        <v>1505.8</v>
       </c>
       <c r="I38" t="n">
         <v>1511.483836896725</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.66</v>
+        <v>-3.45</v>
       </c>
       <c r="L38" t="n">
-        <v>3.47</v>
+        <v>3.74</v>
       </c>
       <c r="M38" t="n">
         <v>0.51</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.34</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45624.55208333334</v>
+        <v>45625.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1498.15</v>
+        <v>1536.35</v>
       </c>
       <c r="I39" t="n">
         <v>1530.444210599955</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>0.51</v>
+        <v>-2.03</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.78</v>
       </c>
       <c r="M39" t="n">
         <v>0.72</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
         <v>-1.21</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>6.14</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45635.55208333334</v>
+        <v>45636.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1471.95</v>
+        <v>1457.15</v>
       </c>
       <c r="I40" t="n">
         <v>1463.67931606306</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.19</v>
+        <v>-5.16</v>
       </c>
       <c r="L40" t="n">
-        <v>4.49</v>
+        <v>5.23</v>
       </c>
       <c r="M40" t="n">
         <v>0.54</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.26</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1471</v>
+        <v>1506.05</v>
       </c>
       <c r="I41" t="n">
         <v>1492.555452882792</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.95</v>
+        <v>-3.36</v>
       </c>
       <c r="L41" t="n">
-        <v>1.77</v>
+        <v>3.49</v>
       </c>
       <c r="M41" t="n">
         <v>1.34</v>
       </c>
       <c r="N41" t="n">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="O41" t="n">
         <v>-1.02</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.31</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1488.45</v>
+        <v>1477.05</v>
       </c>
       <c r="I42" t="n">
         <v>1478.764742241373</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.17</v>
+        <v>-1.93</v>
       </c>
       <c r="L42" t="n">
         <v>3.73</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.32</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1425.9</v>
+        <v>1462.15</v>
       </c>
       <c r="I43" t="n">
         <v>1437.720726993946</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>3.46</v>
+        <v>1.01</v>
       </c>
       <c r="L43" t="n">
         <v>1.4</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.69</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45716.38541666666</v>
+        <v>45716.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1434.3</v>
+        <v>1405</v>
       </c>
       <c r="I44" t="n">
         <v>1416.279439481717</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.9</v>
+        <v>-3.91</v>
       </c>
       <c r="L44" t="n">
-        <v>3.83</v>
+        <v>4.25</v>
       </c>
       <c r="M44" t="n">
         <v>1.83</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>5.74</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1418.75</v>
+        <v>1459.1</v>
       </c>
       <c r="I45" t="n">
         <v>1458.23444320185</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.98</v>
+        <v>-3.85</v>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>3.99</v>
       </c>
       <c r="M45" t="n">
-        <v>0.01</v>
+        <v>0.44</v>
       </c>
       <c r="N45" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="O45" t="n">
         <v>-2.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.04</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45742.38541666666</v>
+        <v>45742.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1481.9</v>
+        <v>1476</v>
       </c>
       <c r="I46" t="n">
         <v>1476.5917338134</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="L46" t="n">
         <v>2.7</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>3.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1468.5</v>
+        <v>1481.9</v>
       </c>
       <c r="I47" t="n">
         <v>1477.90381863878</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="L47" t="n">
         <v>3.2</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.84</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1484.6</v>
+        <v>1480</v>
       </c>
       <c r="I48" t="n">
         <v>1484.476973499752</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="L48" t="n">
         <v>1.18</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.64</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45819.38541666666</v>
+        <v>45819.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1518.5</v>
+        <v>1527.5</v>
       </c>
       <c r="I49" t="n">
         <v>1520.169841811174</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.6</v>
+        <v>-3.21</v>
       </c>
       <c r="L49" t="n">
         <v>4.05</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>3.01</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45827.38541666666</v>
+        <v>45827.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1488.2</v>
+        <v>1480.5</v>
       </c>
       <c r="I50" t="n">
         <v>1481.563125586934</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.57</v>
+        <v>-3.08</v>
       </c>
       <c r="L50" t="n">
         <v>3.11</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.01</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45863.38541666666</v>
+        <v>45863.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1486.3</v>
+        <v>1534</v>
       </c>
       <c r="I51" t="n">
         <v>1506.122735624578</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.39</v>
+        <v>-3.61</v>
       </c>
       <c r="L51" t="n">
-        <v>3.01</v>
+        <v>4.94</v>
       </c>
       <c r="M51" t="n">
         <v>0.58</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.75</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1552</v>
+        <v>1503.5</v>
       </c>
       <c r="I52" t="n">
         <v>1512.595681139782</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>1.17</v>
+        <v>-1.99</v>
       </c>
       <c r="L52" t="n">
         <v>3.16</v>
@@ -3405,7 +4028,7 @@
         <v>1.17</v>
       </c>
       <c r="N52" t="n">
-        <v>0.77</v>
+        <v>3.03</v>
       </c>
       <c r="O52" t="n">
         <v>3.21</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.01</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1520</v>
+        <v>1564</v>
       </c>
       <c r="I53" t="n">
         <v>1541.546546409234</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.1</v>
+        <v>-4.02</v>
       </c>
       <c r="L53" t="n">
-        <v>3.07</v>
+        <v>4.28</v>
       </c>
       <c r="M53" t="n">
         <v>0.33</v>
       </c>
       <c r="N53" t="n">
-        <v>1.17</v>
+        <v>2.63</v>
       </c>
       <c r="O53" t="n">
         <v>-3.03</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.38</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45905.38541666666</v>
+        <v>45905.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1556.3</v>
+        <v>1551.1</v>
       </c>
       <c r="I54" t="n">
         <v>1552.037693771865</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.49</v>
+        <v>-0.82</v>
       </c>
       <c r="L54" t="n">
         <v>2.79</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>3.72</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45939.55208333334</v>
+        <v>45940.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1513.4</v>
+        <v>1559.6</v>
       </c>
       <c r="I55" t="n">
         <v>1547.260090440138</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>2.43</v>
+        <v>-0.55</v>
       </c>
       <c r="L55" t="n">
         <v>2.18</v>
@@ -3576,7 +4235,7 @@
         <v>1.04</v>
       </c>
       <c r="N55" t="n">
-        <v>1.27</v>
+        <v>3.61</v>
       </c>
       <c r="O55" t="n">
         <v>-1.76</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.49</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45954.38541666666</v>
+        <v>45954.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1592</v>
+        <v>1584.6</v>
       </c>
       <c r="I56" t="n">
         <v>1590.707356025248</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="L56" t="n">
         <v>3.38</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.79</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1520.1</v>
+        <v>1535.1</v>
       </c>
       <c r="I57" t="n">
         <v>1525.122882311436</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>73</v>
+        <v>73.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>4.07</v>
+        <v>3.12</v>
       </c>
       <c r="L57" t="n">
         <v>0.58</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>2.88</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46028.55208333334</v>
+        <v>46029.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1530</v>
+        <v>1469.9</v>
       </c>
       <c r="I58" t="n">
         <v>1495.082963857323</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.33</v>
+        <v>-4.25</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>5.22</v>
       </c>
       <c r="M58" t="n">
-        <v>0.02</v>
+        <v>0.92</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O58" t="n">
         <v>0.65</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.87</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46134.55208333334</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1239</v>
+        <v>1290.1</v>
       </c>
       <c r="I59" t="n">
         <v>1247.463649690933</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>105.1666666666667</v>
+        <v>106</v>
       </c>
       <c r="K59" t="n">
-        <v>15.71</v>
+        <v>12.23</v>
       </c>
       <c r="L59" t="n">
         <v>3.14</v>
@@ -3804,7 +4511,7 @@
         <v>3.84</v>
       </c>
       <c r="N59" t="n">
-        <v>2.3</v>
+        <v>5.49</v>
       </c>
       <c r="O59" t="n">
         <v>-4.23</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.47</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1316.8</v>
+        <v>1305.5</v>
       </c>
       <c r="I60" t="n">
         <v>1316.163780137132</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>2.07</v>
+        <v>1.19</v>
       </c>
       <c r="L60" t="n">
         <v>4.84</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.29</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1329.8</v>
+        <v>1418</v>
       </c>
       <c r="I61" t="n">
         <v>1358.615662258128</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.86</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>3.91</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="N61" t="n">
-        <v>2.79</v>
+        <v>7.91</v>
       </c>
       <c r="O61" t="n">
         <v>-3.15</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1394</v>
+        <v>1369.3</v>
       </c>
       <c r="I62" t="n">
         <v>1371.042483213971</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.69</v>
+        <v>-3.43</v>
       </c>
       <c r="L62" t="n">
-        <v>3.94</v>
+        <v>4.22</v>
       </c>
       <c r="M62" t="n">
         <v>1.19</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4.75</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46192.55208333334</v>
+        <v>46195.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1353</v>
+        <v>1411.1</v>
       </c>
       <c r="I63" t="n">
         <v>1399.356720322327</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>1.19</v>
+        <v>-3.05</v>
       </c>
       <c r="L63" t="n">
-        <v>2.69</v>
+        <v>3.24</v>
       </c>
       <c r="M63" t="n">
-        <v>0.77</v>
+        <v>1.4</v>
       </c>
       <c r="N63" t="n">
-        <v>2.26</v>
+        <v>4.73</v>
       </c>
       <c r="O63" t="n">
         <v>-0.72</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.63</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46219.55208333334</v>
+        <v>46220.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1430</v>
+        <v>1411</v>
       </c>
       <c r="I64" t="n">
         <v>1415.761474255409</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>1.34</v>
+        <v>-0.01</v>
       </c>
       <c r="L64" t="n">
         <v>2.87</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>4.32</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1447</v>
+        <v>1484.1</v>
       </c>
       <c r="I65" t="n">
         <v>1465.867679754979</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.55</v>
+        <v>-5.18</v>
       </c>
       <c r="L65" t="n">
-        <v>3.94</v>
+        <v>5.68</v>
       </c>
       <c r="M65" t="n">
         <v>0.83</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>6.89</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46252.55208333334</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1432</v>
+        <v>1418.6</v>
       </c>
       <c r="I66" t="n">
         <v>1421.497134026884</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.51</v>
+        <v>-4.41</v>
       </c>
       <c r="L66" t="n">
-        <v>4.07</v>
+        <v>4.6</v>
       </c>
       <c r="M66" t="n">
         <v>0.42</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>3.23</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46288.55208333334</v>
+        <v>46289.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1377</v>
+        <v>1410.6</v>
       </c>
       <c r="I67" t="n">
         <v>1398.626316923148</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K67" t="n">
-        <v>2.93</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L67" t="n">
         <v>1.76</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>5.48</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1355</v>
+        <v>1339.6</v>
       </c>
       <c r="I68" t="n">
         <v>1348.644885195999</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.94</v>
+        <v>-5.03</v>
       </c>
       <c r="L68" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="M68" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="N68" t="n">
         <v>1.82</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>4.92</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1349.8</v>
+        <v>1366.7</v>
       </c>
       <c r="I69" t="n">
         <v>1352.243103358269</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.76</v>
+        <v>-2.02</v>
       </c>
       <c r="L69" t="n">
-        <v>1.52</v>
+        <v>2.43</v>
       </c>
       <c r="M69" t="n">
         <v>0.89</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,12 @@
       <c r="Q70" t="n">
         <v>4</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +7381,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="6">
@@ -6546,7 +7391,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="7">
@@ -6556,7 +7401,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
@@ -6566,7 +7411,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6576,7 +7421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6586,7 +7431,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="11">
@@ -6596,7 +7441,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -6606,7 +7451,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6616,7 +7461,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6626,7 +7471,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.21</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +7481,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.63</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="16">
@@ -6646,7 +7491,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="17">
@@ -6656,7 +7501,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.88</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="18">
@@ -6666,7 +7511,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.1</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="19">
@@ -6676,7 +7521,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.11</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="20">
@@ -6686,7 +7531,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="21">
@@ -6696,7 +7541,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -6706,7 +7551,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -6726,7 +7571,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.98</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="25">
@@ -6736,7 +7581,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.84</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="26">
@@ -6746,7 +7591,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="27">
@@ -6756,7 +7601,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.2</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="28">
@@ -6766,7 +7611,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
